--- a/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0001T0006Z000C1N47_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0001T0006Z000C1N47_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>33.77266157113942</v>
+        <v>5.488057505310155</v>
       </c>
       <c r="D2" t="n">
-        <v>33.1609706292286</v>
+        <v>5.388657727249647</v>
       </c>
       <c r="E2" t="n">
-        <v>2.921964982865236</v>
+        <v>0.4748193097156013</v>
       </c>
       <c r="F2" t="n">
-        <v>4.043457554973614</v>
+        <v>0.6570618526832123</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>30.12572547067558</v>
+        <v>4.895430388984781</v>
       </c>
       <c r="D3" t="n">
-        <v>31.17450845845672</v>
+        <v>5.065857624499217</v>
       </c>
       <c r="E3" t="n">
-        <v>2.921964982865236</v>
+        <v>0.4748193097156013</v>
       </c>
       <c r="F3" t="n">
-        <v>4.043457554973614</v>
+        <v>0.6570618526832123</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>37.28261174323529</v>
+        <v>6.058424408275735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.76455880509863</v>
+        <v>3.861740805828528</v>
       </c>
       <c r="E4" t="n">
-        <v>2.921964982865236</v>
+        <v>0.4748193097156013</v>
       </c>
       <c r="F4" t="n">
-        <v>4.043457554973614</v>
+        <v>0.6570618526832123</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
